--- a/artfynd/A 37422-2021 artfynd.xlsx
+++ b/artfynd/A 37422-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131532953</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37422-2021 artfynd.xlsx
+++ b/artfynd/A 37422-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131532953</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37422-2021 artfynd.xlsx
+++ b/artfynd/A 37422-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131532953</v>
+        <v>129574926</v>
       </c>
       <c r="B2" t="n">
-        <v>57911</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,48 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Smedhagen, Smedhagen, Srm</t>
+          <t>Backen, Backen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658871</v>
+        <v>658745</v>
       </c>
       <c r="R2" t="n">
-        <v>6534771</v>
+        <v>6534639</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -793,6 +793,253 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129576153</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Backen, Backen, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>658753</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6534562</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp på död tall</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Krister  Sernbo</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Krister  Sernbo</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131532953</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Smedhagen, Smedhagen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>658871</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6534771</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Krister  Sernbo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Krister  Sernbo</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
